--- a/题库模板.xlsx
+++ b/题库模板.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -433,6 +433,210 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>以下哪个选项是Python中正确的变量命名方式？</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A. 123var | B. _myVar | C. my-var | D. class</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HTML中用于定义超链接的标签是？</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A. &lt;link&gt; | B. &lt;href&gt; | C. &lt;a&gt; | D. &lt;url&gt;</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TCP/IP协议中，HTTP协议工作在哪一层？</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A. 应用层 | B. 传输层 | C. 网络层 | D. 数据链路层</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>以下哪些是Python的内置数据类型？（多选）</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A. list | B. dict | C. set | D. int | E. array</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>关系型数据库中，用于查询数据的SQL语句是？</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A. SELECT | B. INSERT | C. UPDATE | D. DELETE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Python中，用于定义函数的关键字是？</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A. def | B. function | C. func | D. define</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>计算机中，1KB等于多少字节？</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A. 512 | B. 1000 | C. 1024 | D. 2048</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>关于面向对象编程，以下说法正确的是？（多选）</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A. 封装 | B. 继承 | C. 多态 | D. 重载</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python是一种编译型语言。</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>正确 | 错误</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HTTPS协议比HTTP协议更安全。</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>正确 | 错误</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>在Python中，列表是不可变类型。</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>正确 | 错误</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Linux系统中，用于查看当前目录文件的命令是？</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A. ls | B. cd | C. dir | D. pwd</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
